--- a/services_forms/001_find_dentist--services_forms.xlsx
+++ b/services_forms/001_find_dentist--services_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -661,7 +661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -915,12 +915,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>san_jose</t>
+          <t>indianapolis</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Jose</t>
+          <t>Indianapolis</t>
         </is>
       </c>
     </row>
@@ -932,46 +932,46 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>indianapolis</t>
+          <t>san_fransisco</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>San Fransisco</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>location_choices</t>
+          <t>dentist_info_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>san_fransisco</t>
+          <t>dentist_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Fransisco</t>
+          <t>Dentist 1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>location_choices</t>
+          <t>dentist_info_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>san_francisco</t>
+          <t>dentist_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Dentist 2</t>
         </is>
       </c>
     </row>
@@ -983,44 +983,10 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>dentist_1</t>
+          <t>dentist_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
-        <is>
-          <t>Dentist 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>dentist_info_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>dentist_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Dentist 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>dentist_info_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>dentist_3</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
         <is>
           <t>Dentist 3</t>
         </is>
